--- a/收藏品全量详表.xlsx
+++ b/收藏品全量详表.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'收藏品总表'!$A$1:$X$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'全参数矩阵'!$A$1:$DC$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'审计与资源'!$A$1:$T$113</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'系统与运行时'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'系统与运行时'!$A$1:$C$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'字段字典'!$A$1:$H$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'测试与引用'!$A$1:$H$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'文案改写记录'!$A$1:$F$7</definedName>
@@ -3223,8 +3223,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RuntimeRules" displayName="RuntimeRules" ref="A1:C13" headerRowCount="1">
-  <autoFilter ref="A1:C13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RuntimeRules" displayName="RuntimeRules" ref="A1:C15" headerRowCount="1">
+  <autoFilter ref="A1:C15"/>
   <tableColumns count="3">
     <tableColumn id="1" name="主题"/>
     <tableColumn id="2" name="代码入口/常量"/>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-11 16:18:19 +0800</t>
+          <t>2026-07-11 17:22:49 +0800</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="inlineStr">
@@ -3828,12 +3828,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>抽取方式</t>
+          <t>每轮洛曦刷新</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>先按当前可用稀有度权重抽稀有度，再在该稀有度收藏品中等概率抽取；同次3选不重复。</t>
+          <t>最多4次，费用依次为100、200、500、1000息壤；下次休整期重置。</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -3854,12 +3854,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>工作簿口径</t>
+          <t>抽取方式</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>有效值=配置显式值，否则使用PickupConfig/审计脚本默认值；底层倍率与自然语言换算同时保留。</t>
+          <t>先按当前可用稀有度权重抽稀有度，再在该稀有度收藏品中等概率抽取；同次3选不重复。</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -3870,8 +3870,16 @@
       <c r="H13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>工作簿口径</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>有效值=配置显式值，否则使用PickupConfig/审计脚本默认值；底层倍率与自然语言换算同时保留。</t>
+        </is>
+      </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -68847,7 +68855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -68936,148 +68944,182 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>每名玩家每段场间时间最多成功领取2次；失败领取不消耗次数。</t>
+          <t>每名玩家每段场间时间最多成功领取1次；失败领取不消耗次数。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>背包</t>
+          <t>付费刷新</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>RunStateStore.INVENTORY_CAPACITY</t>
+          <t>LuoxiMerchant.REFRESH_COSTS</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>每名玩家20格；收藏品必须can_store_in_inventory=true。</t>
+          <t>每段场间最多刷新4次，依次花费100、200、500、1000息壤；由单机游戏或多人主机权威扣费。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>唯一效果</t>
+          <t>刷新重置</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>LuoxiMerchant.is_collectible_available_for_inventory</t>
+          <t>LuoxiMerchant.reset_intermission_state</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>stacks_by_copy=false时，同effect_id已有一份就不会再次提供。</t>
+          <t>进入下一段休整期时同时清空领取计数、刷新计数和候选缓存。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>叠加效果</t>
+          <t>背包</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>collectible_stacks_by_copy / collectible_max_copies</t>
+          <t>RunStateStore.INVENTORY_CAPACITY</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>逐份生效；max_copies=0代表配置不限，实际仍受20格背包限制。</t>
+          <t>每名玩家20格；收藏品必须can_store_in_inventory=true。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>角色兼容</t>
+          <t>唯一效果</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Player.is_collectible_compatible</t>
+          <t>LuoxiMerchant.is_collectible_available_for_inventory</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>requires_projectile_primary_attack=true时，仅普攻可生成投射物的角色可获得。</t>
+          <t>stacks_by_copy=false时，同effect_id已有一份就不会再次提供。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>全量刷新</t>
+          <t>叠加效果</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Player._refresh_collectible_stats</t>
+          <t>collectible_stacks_by_copy / collectible_max_copies</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>从背包聚合静态、条件、息壤动态、概率和防御倍率等效果。</t>
+          <t>逐份生效；max_copies=0代表配置不限，实际仍受20格背包限制。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>联网</t>
+          <t>角色兼容</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>MpGame收藏品RPC/广播路径</t>
+          <t>Player.is_collectible_compatible</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>领取由主机确认；投射物、范围效果、闪电、寒霜、月盾视觉均有多人同步实现。</t>
+          <t>requires_projectile_primary_attack=true时，仅普攻可生成投射物的角色可获得。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>通用运行时审计</t>
+          <t>全量刷新</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>dev_tools/collectible_runtime_audit_smoke_test.gd</t>
+          <t>Player._refresh_collectible_stats</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>遍历全部收藏品，验证字段、聚合属性、触发、命中、击杀、周期和技能效果。</t>
+          <t>从背包聚合静态、条件、息壤动态、概率和防御倍率等效果。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>联网</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>MpGame收藏品RPC/广播路径</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>领取由主机确认；投射物、范围效果、闪电、寒霜、月盾视觉均有多人同步实现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>通用运行时审计</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>dev_tools/collectible_runtime_audit_smoke_test.gd</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>遍历全部收藏品，验证字段、聚合属性、触发、命中、击杀、周期和技能效果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>静态审计</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>dev_tools/audit_collectibles.py</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>检查112件数量、字段逻辑、唯一性、效果组合、图标尺寸/像素/导入文件和设计元数据。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
